--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-13 09:32</t>
+          <t>更新时间: 2026-09-13 12:41</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-13 12:41</t>
+          <t>更新时间: 2026-09-13 13:28</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-13 13:28</t>
+          <t>更新时间: 2026-09-13 15:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-13 15:31</t>
+          <t>更新时间: 2026-09-13 17:02</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-13 17:02</t>
+          <t>更新时间: 2026-09-14 09:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-14 09:33</t>
+          <t>更新时间: 2026-09-14 12:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-14 12:49</t>
+          <t>更新时间: 2026-09-14 13:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-14 13:33</t>
+          <t>更新时间: 2026-09-14 15:58</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-14 15:58</t>
+          <t>更新时间: 2026-09-14 17:35</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-14 17:35</t>
+          <t>更新时间: 2026-09-15 09:48</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-15 09:48</t>
+          <t>更新时间: 2026-09-15 12:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-15 12:49</t>
+          <t>更新时间: 2026-09-15 13:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-15 15:53</t>
+          <t>更新时间: 2026-09-15 17:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-15 17:13</t>
+          <t>更新时间: 2026-09-16 09:42</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-16 09:42</t>
+          <t>更新时间: 2026-09-16 12:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-16 12:45</t>
+          <t>更新时间: 2026-09-16 13:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-16 13:26</t>
+          <t>更新时间: 2026-09-16 15:46</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-16 15:46</t>
+          <t>更新时间: 2026-09-16 17:05</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-16 17:05</t>
+          <t>更新时间: 2026-09-17 09:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-17 09:47</t>
+          <t>更新时间: 2026-09-17 12:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-17 12:47</t>
+          <t>更新时间: 2026-09-17 13:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-17 13:34</t>
+          <t>更新时间: 2026-09-17 15:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-17 15:49</t>
+          <t>更新时间: 2026-09-17 17:14</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-17 17:14</t>
+          <t>更新时间: 2026-09-18 09:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-18 09:31</t>
+          <t>更新时间: 2026-09-18 12:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-18 12:37</t>
+          <t>更新时间: 2026-09-18 13:22</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-18 13:22</t>
+          <t>更新时间: 2026-09-18 15:28</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-18 15:28</t>
+          <t>更新时间: 2026-09-18 16:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-18 16:47</t>
+          <t>更新时间: 2026-09-19 09:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 09:34</t>
+          <t>更新时间: 2026-09-19 12:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 12:32</t>
+          <t>更新时间: 2026-09-19 13:15</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 13:15</t>
+          <t>更新时间: 2026-09-19 15:24</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 15:24</t>
+          <t>更新时间: 2026-09-19 16:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 16:33</t>
+          <t>更新时间: 2026-09-20 09:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 09:33</t>
+          <t>更新时间: 2026-09-20 12:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 12:49</t>
+          <t>更新时间: 2026-09-20 13:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 15:48</t>
+          <t>更新时间: 2026-09-20 17:05</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 17:05</t>
+          <t>更新时间: 2026-09-21 09:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 09:32</t>
+          <t>更新时间: 2026-09-21 12:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 12:50</t>
+          <t>更新时间: 2026-09-21 13:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 13:37</t>
+          <t>更新时间: 2026-09-21 16:02</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 16:02</t>
+          <t>更新时间: 2026-09-21 17:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 17:37</t>
+          <t>更新时间: 2026-09-22 09:55</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 09:55</t>
+          <t>更新时间: 2026-09-22 12:48</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 12:48</t>
+          <t>更新时间: 2026-09-22 13:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 13:34</t>
+          <t>更新时间: 2026-09-22 15:48</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 15:48</t>
+          <t>更新时间: 2026-09-22 17:02</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 17:02</t>
+          <t>更新时间: 2026-09-23 09:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-23 09:51</t>
+          <t>更新时间: 2026-09-23 12:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-23 12:40</t>
+          <t>更新时间: 2026-09-23 13:21</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-23 13:21</t>
+          <t>更新时间: 2026-09-23 15:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-23 15:50</t>
+          <t>更新时间: 2026-09-23 17:06</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-23 17:06</t>
+          <t>更新时间: 2026-09-24 09:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 09:49</t>
+          <t>更新时间: 2026-09-24 12:42</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 12:42</t>
+          <t>更新时间: 2026-09-24 13:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 13:37</t>
+          <t>更新时间: 2026-09-24 15:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 15:40</t>
+          <t>更新时间: 2026-09-24 17:01</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 17:01</t>
+          <t>更新时间: 2026-09-25 09:52</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 09:52</t>
+          <t>更新时间: 2026-09-25 12:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 12:51</t>
+          <t>更新时间: 2026-09-25 13:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 15:58</t>
+          <t>更新时间: 2026-09-25 17:24</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 17:24</t>
+          <t>更新时间: 2026-09-26 09:59</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 09:59</t>
+          <t>更新时间: 2026-09-26 12:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 12:51</t>
+          <t>更新时间: 2026-09-26 13:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 13:40</t>
+          <t>更新时间: 2026-09-26 15:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 15:51</t>
+          <t>更新时间: 2026-09-26 17:09</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 17:09</t>
+          <t>更新时间: 2026-09-27 09:54</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 09:54</t>
+          <t>更新时间: 2026-09-27 13:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 13:13</t>
+          <t>更新时间: 2026-09-27 13:57</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 13:57</t>
+          <t>更新时间: 2026-09-27 16:21</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 16:21</t>
+          <t>更新时间: 2026-09-27 17:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 17:50</t>
+          <t>更新时间: 2026-09-28 10:05</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 10:05</t>
+          <t>更新时间: 2026-09-28 13:17</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 13:17</t>
+          <t>更新时间: 2026-09-28 14:05</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 14:05</t>
+          <t>更新时间: 2026-09-28 16:48</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 16:48</t>
+          <t>更新时间: 2026-09-28 18:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 18:37</t>
+          <t>更新时间: 2026-09-29 10:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-29 10:51</t>
+          <t>更新时间: 2026-09-29 13:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-29 13:38</t>
+          <t>更新时间: 2026-09-29 14:23</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-29 16:43</t>
+          <t>更新时间: 2026-09-29 18:25</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-29 18:25</t>
+          <t>更新时间: 2026-09-30 10:28</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 10:28</t>
+          <t>更新时间: 2026-09-30 13:27</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 13:27</t>
+          <t>更新时间: 2026-09-30 14:07</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 14:07</t>
+          <t>更新时间: 2026-09-30 16:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 16:44</t>
+          <t>更新时间: 2026-09-30 18:18</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 18:18</t>
+          <t>更新时间: 2026-10-01 10:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 10:33</t>
+          <t>更新时间: 2026-10-01 13:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 13:45</t>
+          <t>更新时间: 2026-10-01 14:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 17:06</t>
+          <t>更新时间: 2026-10-01 18:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 18:44</t>
+          <t>更新时间: 2026-10-02 10:35</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 10:35</t>
+          <t>更新时间: 2026-10-02 13:29</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 13:29</t>
+          <t>更新时间: 2026-10-02 14:24</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 14:24</t>
+          <t>更新时间: 2026-10-02 16:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 16:40</t>
+          <t>更新时间: 2026-10-02 18:19</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 18:19</t>
+          <t>更新时间: 2026-10-03 10:23</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 10:23</t>
+          <t>更新时间: 2026-10-03 13:12</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 13:12</t>
+          <t>更新时间: 2026-10-03 13:53</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 16:19</t>
+          <t>更新时间: 2026-10-03 17:41</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 17:41</t>
+          <t>更新时间: 2026-10-04 11:03</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 11:03</t>
+          <t>更新时间: 2026-10-04 13:46</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 13:46</t>
+          <t>更新时间: 2026-10-04 14:30</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 18:25</t>
+          <t>更新时间: 2026-10-05 10:23</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-05 10:23</t>
+          <t>更新时间: 2026-10-05 13:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-05 13:31</t>
+          <t>更新时间: 2026-10-05 14:24</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-05 17:15</t>
+          <t>更新时间: 2026-10-05 19:12</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-05 19:12</t>
+          <t>更新时间: 2026-10-06 11:22</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-06 11:22</t>
+          <t>更新时间: 2026-10-06 14:14</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-06 14:14</t>
+          <t>更新时间: 2026-10-06 14:59</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-06 14:59</t>
+          <t>更新时间: 2026-10-06 17:07</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-06 17:07</t>
+          <t>更新时间: 2026-10-06 19:02</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-06 19:02</t>
+          <t>更新时间: 2026-10-07 10:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-07 10:45</t>
+          <t>更新时间: 2026-10-07 13:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-07 13:51</t>
+          <t>更新时间: 2026-10-07 14:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-07 14:40</t>
+          <t>更新时间: 2026-10-07 16:54</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-07 16:54</t>
+          <t>更新时间: 2026-10-07 18:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-07 18:51</t>
+          <t>更新时间: 2026-10-08 11:00</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-08 11:00</t>
+          <t>更新时间: 2026-10-08 13:56</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-08 13:56</t>
+          <t>更新时间: 2026-10-08 14:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-08 14:47</t>
+          <t>更新时间: 2026-10-08 17:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-08 17:10</t>
+          <t>更新时间: 2026-10-08 19:09</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-08 19:09</t>
+          <t>更新时间: 2026-10-09 11:14</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-09 11:14</t>
+          <t>更新时间: 2026-10-09 14:02</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-09 14:02</t>
+          <t>更新时间: 2026-10-09 14:55</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-09 14:55</t>
+          <t>更新时间: 2026-10-09 17:18</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-09 17:18</t>
+          <t>更新时间: 2026-10-09 19:08</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-09 19:08</t>
+          <t>更新时间: 2026-10-10 10:41</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-10 10:41</t>
+          <t>更新时间: 2026-10-10 13:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-10 13:45</t>
+          <t>更新时间: 2026-10-10 14:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-10 16:40</t>
+          <t>更新时间: 2026-10-10 18:25</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-10 18:25</t>
+          <t>更新时间: 2026-10-11 10:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 10:16</t>
+          <t>更新时间: 2026-10-11 13:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 13:40</t>
+          <t>更新时间: 2026-10-11 14:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 17:04</t>
+          <t>更新时间: 2026-10-11 18:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 18:37</t>
+          <t>更新时间: 2026-10-12 10:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-12 10:44</t>
+          <t>更新时间: 2026-10-12 13:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-12 13:49</t>
+          <t>更新时间: 2026-10-12 14:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-12 14:43</t>
+          <t>更新时间: 2026-10-12 17:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-12 17:26</t>
+          <t>更新时间: 2026-10-12 19:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-12 19:40</t>
+          <t>更新时间: 2026-10-13 11:54</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-13 11:54</t>
+          <t>更新时间: 2026-10-13 14:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-13 14:43</t>
+          <t>更新时间: 2026-10-13 15:12</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-13 17:34</t>
+          <t>更新时间: 2026-10-13 19:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-13 19:26</t>
+          <t>更新时间: 2026-10-14 10:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-14 10:16</t>
+          <t>更新时间: 2026-10-14 12:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-14 12:47</t>
+          <t>更新时间: 2026-10-14 13:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-14 15:48</t>
+          <t>更新时间: 2026-10-14 17:18</t>
         </is>
       </c>
     </row>
